--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1723,6 +1723,339 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113680500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91382</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartsjötjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>657925</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7079009</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113680506</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91388</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>658151</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7078667</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113680499</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90146</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>658211</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7078789</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680500</v>
+        <v>113680506</v>
       </c>
       <c r="B11" t="n">
-        <v>91382</v>
+        <v>91390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,38 +1738,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartsjötjärnen, Ång</t>
+          <t>Bergslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>657925</v>
+        <v>658151</v>
       </c>
       <c r="R11" t="n">
-        <v>7079009</v>
+        <v>7078667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680506</v>
+        <v>113680499</v>
       </c>
       <c r="B12" t="n">
-        <v>91388</v>
+        <v>90148</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,25 +1849,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658151</v>
+        <v>658211</v>
       </c>
       <c r="R12" t="n">
-        <v>7078667</v>
+        <v>7078789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680499</v>
+        <v>113680500</v>
       </c>
       <c r="B13" t="n">
-        <v>90146</v>
+        <v>91384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,34 +1964,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergslåtten, Ång</t>
+          <t>Svartsjötjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658211</v>
+        <v>657925</v>
       </c>
       <c r="R13" t="n">
-        <v>7078789</v>
+        <v>7079009</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -1840,7 +1840,7 @@
         <v>113680499</v>
       </c>
       <c r="B12" t="n">
-        <v>90148</v>
+        <v>90149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680506</v>
+        <v>113680500</v>
       </c>
       <c r="B11" t="n">
-        <v>91390</v>
+        <v>91388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,38 +1738,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergslåtten, Ång</t>
+          <t>Svartsjötjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658151</v>
+        <v>657925</v>
       </c>
       <c r="R11" t="n">
-        <v>7078667</v>
+        <v>7079009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680499</v>
+        <v>113680506</v>
       </c>
       <c r="B12" t="n">
-        <v>90149</v>
+        <v>91394</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,25 +1849,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658211</v>
+        <v>658151</v>
       </c>
       <c r="R12" t="n">
-        <v>7078789</v>
+        <v>7078667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680500</v>
+        <v>113680499</v>
       </c>
       <c r="B13" t="n">
-        <v>91384</v>
+        <v>90153</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,34 +1964,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartsjötjärnen, Ång</t>
+          <t>Bergslåtten, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657925</v>
+        <v>658211</v>
       </c>
       <c r="R13" t="n">
-        <v>7079009</v>
+        <v>7078789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680500</v>
+        <v>113680506</v>
       </c>
       <c r="B11" t="n">
-        <v>91388</v>
+        <v>91394</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,38 +1738,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartsjötjärnen, Ång</t>
+          <t>Bergslåtten, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>657925</v>
+        <v>658151</v>
       </c>
       <c r="R11" t="n">
-        <v>7079009</v>
+        <v>7078667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680506</v>
+        <v>113680500</v>
       </c>
       <c r="B12" t="n">
-        <v>91394</v>
+        <v>91388</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,38 +1849,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergslåtten, Ång</t>
+          <t>Svartsjötjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658151</v>
+        <v>657925</v>
       </c>
       <c r="R12" t="n">
-        <v>7078667</v>
+        <v>7079009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680506</v>
+        <v>113680499</v>
       </c>
       <c r="B11" t="n">
-        <v>91394</v>
+        <v>90153</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,25 +1738,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658151</v>
+        <v>658211</v>
       </c>
       <c r="R11" t="n">
-        <v>7078667</v>
+        <v>7078789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680499</v>
+        <v>113680506</v>
       </c>
       <c r="B13" t="n">
-        <v>90153</v>
+        <v>91394</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658211</v>
+        <v>658151</v>
       </c>
       <c r="R13" t="n">
-        <v>7078789</v>
+        <v>7078667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -1726,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680499</v>
+        <v>113680500</v>
       </c>
       <c r="B11" t="n">
-        <v>90153</v>
+        <v>91388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,34 +1742,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergslåtten, Ång</t>
+          <t>Svartsjötjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658211</v>
+        <v>657925</v>
       </c>
       <c r="R11" t="n">
-        <v>7078789</v>
+        <v>7079009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680500</v>
+        <v>113680506</v>
       </c>
       <c r="B12" t="n">
-        <v>91388</v>
+        <v>91394</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,38 +1849,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartsjötjärnen, Ång</t>
+          <t>Bergslåtten, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657925</v>
+        <v>658151</v>
       </c>
       <c r="R12" t="n">
-        <v>7079009</v>
+        <v>7078667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680506</v>
+        <v>113680499</v>
       </c>
       <c r="B13" t="n">
-        <v>91394</v>
+        <v>90153</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658151</v>
+        <v>658211</v>
       </c>
       <c r="R13" t="n">
-        <v>7078667</v>
+        <v>7078789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680506</v>
+        <v>113680499</v>
       </c>
       <c r="B12" t="n">
-        <v>91394</v>
+        <v>90153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,25 +1849,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658151</v>
+        <v>658211</v>
       </c>
       <c r="R12" t="n">
-        <v>7078667</v>
+        <v>7078789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680499</v>
+        <v>113680506</v>
       </c>
       <c r="B13" t="n">
-        <v>90153</v>
+        <v>91394</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658211</v>
+        <v>658151</v>
       </c>
       <c r="R13" t="n">
-        <v>7078789</v>
+        <v>7078667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 31677-2022 artfynd.xlsx
+++ b/artfynd/A 31677-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
